--- a/TASK2/Scenariji/SC10_AzuriranjeProfilaClan.xlsx
+++ b/TASK2/Scenariji/SC10_AzuriranjeProfilaClan.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Azuriranje profila clana</t>
+          <t>Ažuriranje profila člana</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Clan ili administrator azurira podatke profila clana teretane.</t>
+          <t>Član ili administrator ažurira podatke profila člana teretane.</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Registracija novih clanova sa svim potrebnim podacima</t>
+          <t>Registracija novih članova sa svim potrebnim podacima</t>
         </is>
       </c>
     </row>
@@ -497,31 +497,31 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Korisnik je prijavljen na sistem. Profil clana postoji.</t>
+          <t>Korisnik je prijavljen na sistem. Profil člana postoji.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - uspjesan zavrsetak</t>
+          <t>Posljedice - uspješan završetak</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Profil clana je azuriran, promjene su pohranjene.</t>
+          <t>Profil člana je azuriran, promjene su pohranjene.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - neuspjesan zavrsetak</t>
+          <t>Posljedice - neuspješan završetak</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Azuriranje nije izvrseno zbog nevalidnih podataka ili duplikata.</t>
+          <t>Ažuriranje nije izvršeno zbog nevalidnih podataka ili duplikata.</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Clan teretane / Administrator</t>
+          <t>Član teretane / Administrator</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Korisnik otvara profil, mijenja podatke, sistem validira i azurira.</t>
+          <t>Korisnik otvara profil, mijenja podatke, sistem validira i ažurira.</t>
         </is>
       </c>
     </row>
@@ -569,10 +569,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Nevalidni podaci, Email vec postoji</t>
-        </is>
-      </c>
-    </row>
+          <t>Nevalidni podaci, Email već postoji</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -595,7 +596,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1. Otvaranje profila clana</t>
+          <t>1. Otvaranje profila člana</t>
         </is>
       </c>
     </row>
@@ -644,17 +645,18 @@
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>8. Azuriranje profila u bazi podataka</t>
+          <t>8. Ažuriranje profila u bazi podataka</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>9. Prikaz potvrde azuriranja</t>
-        </is>
-      </c>
-    </row>
+          <t>9. Prikaz potvrde ažuriranja</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -702,10 +704,11 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Alternativni Tok - Email vec postoji</t>
+          <t>Alternativni Tok - Email već postoji</t>
         </is>
       </c>
     </row>
@@ -731,7 +734,7 @@
     <row r="34">
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>7b. Prikaz poruke da email vec postoji</t>
+          <t>7b. Prikaz poruke da email već postoji</t>
         </is>
       </c>
     </row>
